--- a/data/trans_camb/P11_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P11_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 1,28</t>
+          <t>-7,57; 0,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 2,85</t>
+          <t>-6,16; 2,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,18; 13,91</t>
+          <t>4,21; 13,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 9,58</t>
+          <t>-1,18; 9,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 7,51</t>
+          <t>-2,41; 8,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,74; 14,57</t>
+          <t>5,74; 14,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 3,78</t>
+          <t>-2,82; 3,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 3,94</t>
+          <t>-2,68; 4,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 12,9</t>
+          <t>6,1; 13,01</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,39; 6,63</t>
+          <t>-31,16; 3,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,08; 14,51</t>
+          <t>-25,61; 11,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,93; 69,62</t>
+          <t>17,94; 67,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 34,81</t>
+          <t>-3,84; 35,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 27,47</t>
+          <t>-7,19; 31,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,0; 52,5</t>
+          <t>17,89; 55,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 15,36</t>
+          <t>-10,1; 15,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 16,19</t>
+          <t>-9,8; 17,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,19; 52,82</t>
+          <t>22,33; 53,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 8,67</t>
+          <t>1,31; 8,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 6,63</t>
+          <t>-0,38; 6,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 9,55</t>
+          <t>-6,59; 9,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,96</t>
+          <t>0,75; 8,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 7,92</t>
+          <t>-0,65; 8,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,16; 15,02</t>
+          <t>7,54; 15,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 7,68</t>
+          <t>2,37; 7,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,85</t>
+          <t>0,76; 6,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 11,09</t>
+          <t>-2,54; 10,89</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,1; 62,65</t>
+          <t>7,25; 61,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 48,47</t>
+          <t>-2,92; 45,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,77; 64,15</t>
+          <t>-40,11; 64,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 36,85</t>
+          <t>2,56; 35,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 32,15</t>
+          <t>-1,96; 32,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,23; 62,61</t>
+          <t>25,52; 63,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,25; 39,09</t>
+          <t>10,86; 39,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 29,04</t>
+          <t>3,24; 31,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 54,28</t>
+          <t>-12,11; 52,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,91; -2,0</t>
+          <t>-9,93; -1,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 2,14</t>
+          <t>-5,92; 2,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 9,42</t>
+          <t>-0,18; 8,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,07; -2,3</t>
+          <t>-11,44; -1,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,13; -3,16</t>
+          <t>-13,2; -3,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 36,57</t>
+          <t>-6,81; 40,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,53; -3,02</t>
+          <t>-9,53; -2,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,62; -2,23</t>
+          <t>-8,53; -2,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 30,85</t>
+          <t>-1,06; 29,23</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,57; -11,48</t>
+          <t>-46,27; -9,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,51; 12,25</t>
+          <t>-28,02; 15,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 54,54</t>
+          <t>-0,69; 52,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,21; -7,18</t>
+          <t>-30,22; -5,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,5; -9,52</t>
+          <t>-35,38; -10,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 108,98</t>
+          <t>-18,79; 119,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,47; -11,78</t>
+          <t>-33,07; -11,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,78; -8,72</t>
+          <t>-29,57; -7,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 119,59</t>
+          <t>-4,0; 114,15</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 7,72</t>
+          <t>0,55; 8,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 4,52</t>
+          <t>-2,75; 4,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,73; 15,27</t>
+          <t>7,58; 15,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 8,8</t>
+          <t>0,81; 8,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 3,78</t>
+          <t>-4,24; 3,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,95; 15,1</t>
+          <t>2,45; 15,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,92</t>
+          <t>1,52; 7,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 2,72</t>
+          <t>-2,53; 3,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,02; 14,34</t>
+          <t>7,26; 13,99</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,88; 49,58</t>
+          <t>2,51; 52,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 30,33</t>
+          <t>-14,77; 29,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41,46; 99,59</t>
+          <t>39,11; 100,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 35,3</t>
+          <t>2,78; 34,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 14,96</t>
+          <t>-14,41; 14,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,91; 59,68</t>
+          <t>9,65; 59,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,81; 32,41</t>
+          <t>5,74; 33,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 13,15</t>
+          <t>-10,57; 14,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31,72; 68,52</t>
+          <t>31,54; 66,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,72</t>
+          <t>-1,11; 2,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,4</t>
+          <t>-1,34; 2,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,42</t>
+          <t>0,97; 9,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,38</t>
+          <t>-0,06; 4,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,66</t>
+          <t>-2,61; 1,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,26; 22,25</t>
+          <t>6,38; 22,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,91</t>
+          <t>0,03; 2,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,49</t>
+          <t>-1,37; 1,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,51; 15,81</t>
+          <t>5,71; 15,21</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 15,82</t>
+          <t>-5,86; 14,92</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 14,26</t>
+          <t>-7,04; 13,51</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6,22; 53,24</t>
+          <t>6,48; 55,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 15,5</t>
+          <t>-0,1; 15,6</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 5,84</t>
+          <t>-8,68; 6,91</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,23; 78,83</t>
+          <t>21,61; 76,75</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 12,62</t>
+          <t>0,27; 12,91</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 6,54</t>
+          <t>-5,58; 6,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>22,45; 65,63</t>
+          <t>23,19; 66,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P11_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P11_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,74</t>
+          <t>8,5</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,29</t>
+          <t>9,51</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9,68</t>
+          <t>9,16</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 0,63</t>
+          <t>-7,62; 0,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 2,39</t>
+          <t>-5,99; 2,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 13,53</t>
+          <t>3,78; 13,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 9,51</t>
+          <t>-0,95; 8,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 8,33</t>
+          <t>-2,21; 7,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,74; 14,91</t>
+          <t>4,9; 13,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 3,72</t>
+          <t>-2,94; 3,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 4,17</t>
+          <t>-2,93; 3,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,1; 13,01</t>
+          <t>5,99; 12,65</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,16; 3,13</t>
+          <t>-31,17; 4,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,61; 11,8</t>
+          <t>-25,43; 14,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,94; 67,51</t>
+          <t>15,62; 67,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 35,09</t>
+          <t>-2,98; 32,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 31,16</t>
+          <t>-6,96; 28,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,89; 55,1</t>
+          <t>14,96; 48,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 15,05</t>
+          <t>-10,67; 14,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 17,1</t>
+          <t>-10,77; 15,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,33; 53,58</t>
+          <t>21,15; 51,77</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,67</t>
+          <t>8,34</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,26</t>
+          <t>10,63</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,43</t>
+          <t>9,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 8,71</t>
+          <t>1,59; 8,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 6,45</t>
+          <t>-0,67; 6,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 9,88</t>
+          <t>4,5; 11,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 8,88</t>
+          <t>0,5; 8,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 8,08</t>
+          <t>-0,78; 7,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,54; 15,42</t>
+          <t>6,68; 14,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 7,68</t>
+          <t>2,25; 7,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,19</t>
+          <t>0,53; 6,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 10,89</t>
+          <t>6,81; 12,24</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>45,08%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 61,97</t>
+          <t>8,68; 63,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 45,87</t>
+          <t>-4,12; 45,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,11; 64,92</t>
+          <t>24,86; 85,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 35,4</t>
+          <t>1,81; 35,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 32,96</t>
+          <t>-2,73; 29,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,52; 63,19</t>
+          <t>23,26; 60,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,86; 39,71</t>
+          <t>9,29; 37,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 31,31</t>
+          <t>2,63; 30,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 52,43</t>
+          <t>30,67; 62,45</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,64</t>
+          <t>4,7</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,23</t>
+          <t>-4,38</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8,89</t>
+          <t>0,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,93; -1,74</t>
+          <t>-10,28; -2,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 2,66</t>
+          <t>-6,2; 1,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 8,92</t>
+          <t>0,06; 9,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,44; -1,75</t>
+          <t>-11,87; -2,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,2; -3,52</t>
+          <t>-13,44; -3,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 40,58</t>
+          <t>-8,49; 0,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,53; -2,99</t>
+          <t>-9,51; -3,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,53; -2,01</t>
+          <t>-8,68; -1,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 29,23</t>
+          <t>-3,03; 3,44</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>-12,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,27; -9,12</t>
+          <t>-47,47; -13,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,02; 15,37</t>
+          <t>-28,54; 11,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 52,59</t>
+          <t>-0,57; 52,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,22; -5,0</t>
+          <t>-32,11; -6,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,38; -10,86</t>
+          <t>-35,88; -11,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 119,53</t>
+          <t>-23,15; 0,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,07; -11,47</t>
+          <t>-32,98; -12,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,57; -7,8</t>
+          <t>-29,76; -6,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 114,15</t>
+          <t>-10,61; 13,67</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11,57</t>
+          <t>11,05</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,62</t>
+          <t>12,91</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,23</t>
+          <t>12,1</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 8,12</t>
+          <t>0,59; 7,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 4,48</t>
+          <t>-2,53; 4,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,58; 15,7</t>
+          <t>7,37; 15,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,5</t>
+          <t>0,34; 8,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 3,54</t>
+          <t>-4,48; 3,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,45; 15,09</t>
+          <t>9,31; 16,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 7,16</t>
+          <t>1,85; 7,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 3,0</t>
+          <t>-2,24; 2,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,26; 13,99</t>
+          <t>9,31; 14,86</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>53,95%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,51; 52,25</t>
+          <t>3,04; 49,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 29,28</t>
+          <t>-13,59; 27,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39,11; 100,93</t>
+          <t>39,18; 100,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,78; 34,06</t>
+          <t>1,23; 32,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 14,16</t>
+          <t>-15,5; 13,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,65; 59,31</t>
+          <t>32,21; 67,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,74; 33,12</t>
+          <t>7,66; 33,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 14,12</t>
+          <t>-9,38; 13,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31,54; 66,42</t>
+          <t>39,08; 71,49</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6,69</t>
+          <t>8,27</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,0</t>
+          <t>7,93</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,98</t>
+          <t>8,16</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,62</t>
+          <t>-1,23; 2,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,31</t>
+          <t>-1,61; 2,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 9,5</t>
+          <t>6,12; 10,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,39</t>
+          <t>-0,24; 4,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,93</t>
+          <t>-2,73; 1,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,38; 22,0</t>
+          <t>5,7; 9,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,94</t>
+          <t>-0,13; 2,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,51</t>
+          <t>-1,48; 1,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,71; 15,21</t>
+          <t>6,68; 9,73</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 14,92</t>
+          <t>-6,4; 15,18</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 13,51</t>
+          <t>-8,49; 12,95</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6,48; 55,0</t>
+          <t>31,52; 58,28</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 15,6</t>
+          <t>-0,81; 15,43</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 6,91</t>
+          <t>-9,02; 6,03</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,61; 76,75</t>
+          <t>18,85; 35,22</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,27; 12,91</t>
+          <t>-0,57; 12,3</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 6,51</t>
+          <t>-5,99; 6,77</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>23,19; 66,02</t>
+          <t>27,2; 42,52</t>
         </is>
       </c>
     </row>
